--- a/output/pdf_financials_xlsx/TALA.xlsx
+++ b/output/pdf_financials_xlsx/TALA.xlsx
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.14337</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.363279</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.717811</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.739969</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>15.817284</v>
       </c>
     </row>
     <row r="93">
@@ -4680,7 +4680,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5212,7 +5216,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -5906,7 +5914,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>1e-06</v>
       </c>

--- a/output/pdf_financials_xlsx/TALA.xlsx
+++ b/output/pdf_financials_xlsx/TALA.xlsx
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.075987</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.415241</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.318933</v>
       </c>
     </row>
     <row r="13">
@@ -1109,13 +1109,13 @@
         <v>-2.241252</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.296926</v>
+        <v>-2.372913</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-13.840377</v>
+        <v>-14.255618</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-10.251393</v>
+        <v>-10.570326</v>
       </c>
     </row>
     <row r="28">
@@ -1159,13 +1159,13 @@
         <v>-2.241252</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.296926</v>
+        <v>-2.372913</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-13.840377</v>
+        <v>-14.255618</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-10.251393</v>
+        <v>-10.570326</v>
       </c>
     </row>
     <row r="30">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.898566</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.816249</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.167968</v>
@@ -1296,7 +1296,7 @@
         <v>5.575071</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>56.864178</v>
       </c>
     </row>
     <row r="35">
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.898566</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.816249</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.167968</v>
@@ -1346,7 +1346,7 @@
         <v>5.575071</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.30845</v>
+        <v>59.172628</v>
       </c>
     </row>
     <row r="37">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.907066</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.829201</v>
+        <v>0.012952</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.314616</v>
@@ -1646,7 +1646,7 @@
         <v>0.111032</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>57.019805</v>
+        <v>0.155627</v>
       </c>
     </row>
     <row r="49">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">

--- a/output/pdf_financials_xlsx/TALA.xlsx
+++ b/output/pdf_financials_xlsx/TALA.xlsx
@@ -577,19 +577,19 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.148367</v>
+        <v>0.2817</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.541195</v>
+        <v>0.995328</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.043543</v>
+        <v>0.163543</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.013656</v>
+        <v>2.606163</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.619584</v>
+        <v>2.002173</v>
       </c>
     </row>
     <row r="8">
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.027265</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01276</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.042615</v>
@@ -3106,10 +3106,10 @@
         <v>0.001199</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.320611</v>
+        <v>-0.347876</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.048214</v>
+        <v>-0.060974</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.570527</v>
@@ -6236,7 +6236,11 @@
           <t>Deferred income tax expense 20</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -10634,7 +10638,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -10676,7 +10684,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -11938,7 +11950,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -12030,7 +12046,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
         <v>0.002</v>
       </c>
@@ -14132,7 +14152,11 @@
           <t>Salaries, management and director fees 19</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -15086,7 +15110,11 @@
           <t>Salaries, management and director fees 14</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -15498,7 +15526,11 @@
           <t>Management and director fees 7</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
